--- a/月ノルマ/月間週次実績表_2026年8月版.xlsx
+++ b/月ノルマ/月間週次実績表_2026年8月版.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8月予定表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="8月予定表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,9 +730,9 @@
     <row r="3" ht="68" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>勤務日:日勤14日 × 7.5時間 = 105時間(残業なし)
-院内勤務日(9日):8/3(月)・8/7(金)・8/8(土)・8/12(水)・8/13(木)・8/15(土)・8/24(月)・8/25(火・スマートワーキング)・8/26(水・コア会議) — ヒアリング・情報収集・定例・日課
-自宅作業日(5日):8/4(火)・8/5(水)・8/14(金)・8/27(木)・8/28(金) — 健診センターシステム・動画修正(在宅の方が作業がはかどるため)。時間外の自宅勤務は行わない
+          <t>勤務日:日勤14日 × 7.5時間 = 105時間 + 残業13.0時間(在宅日のみ計上)= 118.0時間
+院内勤務日(8日):8/3(月)・8/4(火)・8/8(土)・8/12(水)・8/13(木)・8/15(土)・8/25(火・スマートワーキング)・8/26(水・コア会議) — ヒアリング・情報収集・定例・日課
+自宅作業日(6日):8/5(水)・8/7(金)・8/14(金)・8/24(月)・8/27(木)・8/28(金) — 健診センターシステム・動画修正(在宅の方が作業がはかどるため)。時間外の自宅勤務は行わない
 ※院内勤務日はマネージャーへの進捗状況確認に時間を要する(土曜8/8・8/15はマネージャー休みのため対象外)</t>
         </is>
       </c>
